--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-informant.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
